--- a/نتایج/0110BC01.xlsx
+++ b/نتایج/0110BC01.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RCM\نتایج\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haddadnia\Documents\GitHub\RCM_data_concatinating\نتایج\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -3317,6 +3317,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3344,20 +3358,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3372,8 +3372,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K562" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:K562"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K562" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:K562">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="10"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="11">
     <tableColumn id="1" name="AssetNumber"/>
     <tableColumn id="2" name="TagNo"/>
@@ -3729,7 +3735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" hidden="1">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -3746,7 +3752,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" hidden="1">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -3766,7 +3772,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" hidden="1">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -3786,7 +3792,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" hidden="1">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -3806,7 +3812,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" hidden="1">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -3826,7 +3832,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" hidden="1">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -3846,7 +3852,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" hidden="1">
       <c r="B8" t="s">
         <v>11</v>
       </c>
@@ -3866,7 +3872,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" hidden="1">
       <c r="B9" t="s">
         <v>12</v>
       </c>
@@ -3886,7 +3892,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" hidden="1">
       <c r="B10" t="s">
         <v>13</v>
       </c>
@@ -3906,7 +3912,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" hidden="1">
       <c r="B11" t="s">
         <v>14</v>
       </c>
@@ -3926,7 +3932,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" hidden="1">
       <c r="B12" t="s">
         <v>15</v>
       </c>
@@ -3946,7 +3952,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" hidden="1">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -3966,7 +3972,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" hidden="1">
       <c r="B14" t="s">
         <v>17</v>
       </c>
@@ -3986,7 +3992,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" hidden="1">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -4006,7 +4012,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" hidden="1">
       <c r="B16" t="s">
         <v>19</v>
       </c>
@@ -4026,7 +4032,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" hidden="1">
       <c r="B17" t="s">
         <v>20</v>
       </c>
@@ -4046,7 +4052,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" hidden="1">
       <c r="B18" t="s">
         <v>21</v>
       </c>
@@ -4066,7 +4072,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" hidden="1">
       <c r="B19" t="s">
         <v>22</v>
       </c>
@@ -4086,7 +4092,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" hidden="1">
       <c r="B20" t="s">
         <v>23</v>
       </c>
@@ -4106,7 +4112,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" hidden="1">
       <c r="B21" t="s">
         <v>24</v>
       </c>
@@ -4126,7 +4132,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" hidden="1">
       <c r="B22" t="s">
         <v>25</v>
       </c>
@@ -4146,7 +4152,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" hidden="1">
       <c r="B23" t="s">
         <v>26</v>
       </c>
@@ -4166,7 +4172,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" hidden="1">
       <c r="B24" t="s">
         <v>27</v>
       </c>
@@ -4186,7 +4192,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" hidden="1">
       <c r="B25" t="s">
         <v>28</v>
       </c>
@@ -4206,7 +4212,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" hidden="1">
       <c r="B26" t="s">
         <v>29</v>
       </c>
@@ -4226,7 +4232,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" hidden="1">
       <c r="B27" t="s">
         <v>30</v>
       </c>
@@ -4246,7 +4252,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" hidden="1">
       <c r="B28" t="s">
         <v>31</v>
       </c>
@@ -4266,7 +4272,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" hidden="1">
       <c r="B29" t="s">
         <v>32</v>
       </c>
@@ -4286,7 +4292,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" hidden="1">
       <c r="B30" t="s">
         <v>33</v>
       </c>
@@ -4306,7 +4312,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" hidden="1">
       <c r="B31" t="s">
         <v>34</v>
       </c>
@@ -4326,7 +4332,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" hidden="1">
       <c r="B32" t="s">
         <v>35</v>
       </c>
@@ -4346,7 +4352,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" hidden="1">
       <c r="B33" t="s">
         <v>36</v>
       </c>
@@ -4366,7 +4372,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" hidden="1">
       <c r="B34" t="s">
         <v>37</v>
       </c>
@@ -4386,7 +4392,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" hidden="1">
       <c r="B35" t="s">
         <v>38</v>
       </c>
@@ -4406,7 +4412,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" hidden="1">
       <c r="B36" t="s">
         <v>39</v>
       </c>
@@ -4426,7 +4432,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:9" hidden="1">
       <c r="B37" t="s">
         <v>40</v>
       </c>
@@ -4446,7 +4452,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:9" hidden="1">
       <c r="B38" t="s">
         <v>41</v>
       </c>
@@ -4466,7 +4472,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="39" spans="2:9">
+    <row r="39" spans="2:9" hidden="1">
       <c r="B39" t="s">
         <v>11</v>
       </c>
@@ -4486,7 +4492,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:9" hidden="1">
       <c r="B40" t="s">
         <v>11</v>
       </c>
@@ -4509,7 +4515,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="41" spans="2:9">
+    <row r="41" spans="2:9" hidden="1">
       <c r="B41" t="s">
         <v>11</v>
       </c>
@@ -4532,7 +4538,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:9" hidden="1">
       <c r="B42" t="s">
         <v>11</v>
       </c>
@@ -4555,7 +4561,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" hidden="1">
       <c r="B43" t="s">
         <v>11</v>
       </c>
@@ -4578,7 +4584,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:9" hidden="1">
       <c r="B44" t="s">
         <v>11</v>
       </c>
@@ -4601,7 +4607,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" hidden="1">
       <c r="B45" t="s">
         <v>11</v>
       </c>
@@ -4624,7 +4630,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:9" hidden="1">
       <c r="B46" t="s">
         <v>11</v>
       </c>
@@ -4647,7 +4653,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" hidden="1">
       <c r="B47" t="s">
         <v>11</v>
       </c>
@@ -4670,7 +4676,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" hidden="1">
       <c r="B48" t="s">
         <v>11</v>
       </c>
@@ -4693,7 +4699,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="49" spans="2:9">
+    <row r="49" spans="2:9" hidden="1">
       <c r="B49" t="s">
         <v>11</v>
       </c>
@@ -4716,7 +4722,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="50" spans="2:9">
+    <row r="50" spans="2:9" hidden="1">
       <c r="B50" t="s">
         <v>11</v>
       </c>
@@ -4739,7 +4745,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="51" spans="2:9">
+    <row r="51" spans="2:9" hidden="1">
       <c r="B51" t="s">
         <v>11</v>
       </c>
@@ -4762,7 +4768,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="52" spans="2:9">
+    <row r="52" spans="2:9" hidden="1">
       <c r="B52" t="s">
         <v>11</v>
       </c>
@@ -4785,7 +4791,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="53" spans="2:9">
+    <row r="53" spans="2:9" hidden="1">
       <c r="B53" t="s">
         <v>11</v>
       </c>
@@ -4808,7 +4814,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="54" spans="2:9">
+    <row r="54" spans="2:9" hidden="1">
       <c r="B54" t="s">
         <v>11</v>
       </c>
@@ -4831,7 +4837,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="55" spans="2:9">
+    <row r="55" spans="2:9" hidden="1">
       <c r="B55" t="s">
         <v>11</v>
       </c>
@@ -4851,7 +4857,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="56" spans="2:9">
+    <row r="56" spans="2:9" hidden="1">
       <c r="B56" t="s">
         <v>11</v>
       </c>
@@ -4871,7 +4877,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="57" spans="2:9">
+    <row r="57" spans="2:9" hidden="1">
       <c r="B57" t="s">
         <v>11</v>
       </c>
@@ -4891,7 +4897,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="58" spans="2:9">
+    <row r="58" spans="2:9" hidden="1">
       <c r="B58" t="s">
         <v>11</v>
       </c>
@@ -4911,7 +4917,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="59" spans="2:9">
+    <row r="59" spans="2:9" hidden="1">
       <c r="B59" t="s">
         <v>11</v>
       </c>
@@ -4931,7 +4937,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="60" spans="2:9">
+    <row r="60" spans="2:9" hidden="1">
       <c r="B60" t="s">
         <v>11</v>
       </c>
@@ -4951,7 +4957,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="61" spans="2:9">
+    <row r="61" spans="2:9" hidden="1">
       <c r="B61" t="s">
         <v>11</v>
       </c>
@@ -4971,7 +4977,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="62" spans="2:9">
+    <row r="62" spans="2:9" hidden="1">
       <c r="B62" t="s">
         <v>11</v>
       </c>
@@ -4991,7 +4997,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="63" spans="2:9">
+    <row r="63" spans="2:9" hidden="1">
       <c r="B63" t="s">
         <v>11</v>
       </c>
@@ -5011,7 +5017,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="64" spans="2:9">
+    <row r="64" spans="2:9" hidden="1">
       <c r="B64" t="s">
         <v>11</v>
       </c>
@@ -5031,7 +5037,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
+    <row r="65" spans="2:8" hidden="1">
       <c r="B65" t="s">
         <v>11</v>
       </c>
@@ -5051,7 +5057,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
+    <row r="66" spans="2:8" hidden="1">
       <c r="B66" t="s">
         <v>11</v>
       </c>
@@ -5071,7 +5077,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
+    <row r="67" spans="2:8" hidden="1">
       <c r="B67" t="s">
         <v>11</v>
       </c>
@@ -5091,7 +5097,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
+    <row r="68" spans="2:8" hidden="1">
       <c r="B68" t="s">
         <v>11</v>
       </c>
@@ -5111,7 +5117,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="69" spans="2:8">
+    <row r="69" spans="2:8" hidden="1">
       <c r="B69" t="s">
         <v>11</v>
       </c>
@@ -5131,7 +5137,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="70" spans="2:8">
+    <row r="70" spans="2:8" hidden="1">
       <c r="B70" t="s">
         <v>11</v>
       </c>
@@ -5151,7 +5157,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="71" spans="2:8">
+    <row r="71" spans="2:8" hidden="1">
       <c r="B71" t="s">
         <v>11</v>
       </c>
@@ -5171,7 +5177,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="72" spans="2:8">
+    <row r="72" spans="2:8" hidden="1">
       <c r="B72" t="s">
         <v>11</v>
       </c>
@@ -5191,7 +5197,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="73" spans="2:8">
+    <row r="73" spans="2:8" hidden="1">
       <c r="B73" t="s">
         <v>11</v>
       </c>
@@ -5211,7 +5217,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="74" spans="2:8">
+    <row r="74" spans="2:8" hidden="1">
       <c r="B74" t="s">
         <v>11</v>
       </c>
@@ -5231,7 +5237,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="75" spans="2:8">
+    <row r="75" spans="2:8" hidden="1">
       <c r="B75" t="s">
         <v>11</v>
       </c>
@@ -5251,7 +5257,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="76" spans="2:8">
+    <row r="76" spans="2:8" hidden="1">
       <c r="B76" t="s">
         <v>11</v>
       </c>
@@ -5271,7 +5277,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="77" spans="2:8">
+    <row r="77" spans="2:8" hidden="1">
       <c r="B77" t="s">
         <v>11</v>
       </c>
@@ -5291,7 +5297,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="78" spans="2:8">
+    <row r="78" spans="2:8" hidden="1">
       <c r="B78" t="s">
         <v>11</v>
       </c>
@@ -5311,7 +5317,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="79" spans="2:8">
+    <row r="79" spans="2:8" hidden="1">
       <c r="B79" t="s">
         <v>11</v>
       </c>
@@ -5331,7 +5337,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="80" spans="2:8">
+    <row r="80" spans="2:8" hidden="1">
       <c r="B80" t="s">
         <v>11</v>
       </c>
@@ -5351,7 +5357,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" spans="2:8" hidden="1">
       <c r="B81" t="s">
         <v>11</v>
       </c>
@@ -5371,7 +5377,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" hidden="1">
       <c r="B82" t="s">
         <v>11</v>
       </c>
@@ -5391,7 +5397,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="83" spans="2:8">
+    <row r="83" spans="2:8" hidden="1">
       <c r="B83" t="s">
         <v>11</v>
       </c>
@@ -5411,7 +5417,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" hidden="1">
       <c r="B84" t="s">
         <v>11</v>
       </c>
@@ -5431,7 +5437,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="85" spans="2:8">
+    <row r="85" spans="2:8" hidden="1">
       <c r="B85" t="s">
         <v>11</v>
       </c>
@@ -5451,7 +5457,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" hidden="1">
       <c r="B86" t="s">
         <v>11</v>
       </c>
@@ -5471,7 +5477,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="87" spans="2:8">
+    <row r="87" spans="2:8" hidden="1">
       <c r="B87" t="s">
         <v>11</v>
       </c>
@@ -5491,7 +5497,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="88" spans="2:8">
+    <row r="88" spans="2:8" hidden="1">
       <c r="B88" t="s">
         <v>11</v>
       </c>
@@ -5511,7 +5517,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="89" spans="2:8">
+    <row r="89" spans="2:8" hidden="1">
       <c r="B89" t="s">
         <v>11</v>
       </c>
@@ -5531,7 +5537,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" hidden="1">
       <c r="B90" t="s">
         <v>11</v>
       </c>
@@ -5551,7 +5557,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" hidden="1">
       <c r="B91" t="s">
         <v>11</v>
       </c>
@@ -5871,7 +5877,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="107" spans="2:8">
+    <row r="107" spans="2:8" hidden="1">
       <c r="B107" t="s">
         <v>11</v>
       </c>
@@ -5891,7 +5897,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="108" spans="2:8">
+    <row r="108" spans="2:8" hidden="1">
       <c r="B108" t="s">
         <v>11</v>
       </c>
@@ -5911,7 +5917,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="109" spans="2:8">
+    <row r="109" spans="2:8" hidden="1">
       <c r="B109" t="s">
         <v>11</v>
       </c>
@@ -5931,7 +5937,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="110" spans="2:8">
+    <row r="110" spans="2:8" hidden="1">
       <c r="B110" t="s">
         <v>11</v>
       </c>
@@ -5951,7 +5957,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="111" spans="2:8">
+    <row r="111" spans="2:8" hidden="1">
       <c r="B111" t="s">
         <v>11</v>
       </c>
@@ -5971,7 +5977,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="112" spans="2:8">
+    <row r="112" spans="2:8" hidden="1">
       <c r="B112" t="s">
         <v>11</v>
       </c>
@@ -5991,7 +5997,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="113" spans="2:8">
+    <row r="113" spans="2:8" hidden="1">
       <c r="B113" t="s">
         <v>11</v>
       </c>
@@ -6011,7 +6017,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="114" spans="2:8">
+    <row r="114" spans="2:8" hidden="1">
       <c r="B114" t="s">
         <v>11</v>
       </c>
@@ -6031,7 +6037,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="115" spans="2:8">
+    <row r="115" spans="2:8" hidden="1">
       <c r="B115" t="s">
         <v>11</v>
       </c>
@@ -6051,7 +6057,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="116" spans="2:8">
+    <row r="116" spans="2:8" hidden="1">
       <c r="B116" t="s">
         <v>11</v>
       </c>
@@ -6071,7 +6077,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="117" spans="2:8">
+    <row r="117" spans="2:8" hidden="1">
       <c r="B117" t="s">
         <v>11</v>
       </c>
@@ -6211,7 +6217,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="124" spans="2:8">
+    <row r="124" spans="2:8" hidden="1">
       <c r="B124" t="s">
         <v>11</v>
       </c>
@@ -6571,7 +6577,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="142" spans="2:9">
+    <row r="142" spans="2:9" hidden="1">
       <c r="B142" t="s">
         <v>11</v>
       </c>
@@ -6591,7 +6597,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="143" spans="2:9">
+    <row r="143" spans="2:9" hidden="1">
       <c r="B143" t="s">
         <v>11</v>
       </c>
@@ -6611,7 +6617,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="144" spans="2:9">
+    <row r="144" spans="2:9" hidden="1">
       <c r="B144" t="s">
         <v>11</v>
       </c>
@@ -6634,7 +6640,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="145" spans="2:9">
+    <row r="145" spans="2:9" hidden="1">
       <c r="B145" t="s">
         <v>11</v>
       </c>
@@ -6657,7 +6663,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="146" spans="2:9">
+    <row r="146" spans="2:9" hidden="1">
       <c r="B146" t="s">
         <v>11</v>
       </c>
@@ -6680,7 +6686,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="147" spans="2:9">
+    <row r="147" spans="2:9" hidden="1">
       <c r="B147" t="s">
         <v>11</v>
       </c>
@@ -6703,7 +6709,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="148" spans="2:9">
+    <row r="148" spans="2:9" hidden="1">
       <c r="B148" t="s">
         <v>11</v>
       </c>
@@ -6726,7 +6732,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="149" spans="2:9">
+    <row r="149" spans="2:9" hidden="1">
       <c r="B149" t="s">
         <v>11</v>
       </c>
@@ -6749,7 +6755,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="150" spans="2:9">
+    <row r="150" spans="2:9" hidden="1">
       <c r="B150" t="s">
         <v>11</v>
       </c>
@@ -6772,7 +6778,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="151" spans="2:9">
+    <row r="151" spans="2:9" hidden="1">
       <c r="B151" t="s">
         <v>11</v>
       </c>
@@ -6795,7 +6801,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="152" spans="2:9">
+    <row r="152" spans="2:9" hidden="1">
       <c r="B152" t="s">
         <v>11</v>
       </c>
@@ -6923,7 +6929,7 @@
         <v>155</v>
       </c>
       <c r="D158" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E158">
         <v>10</v>
@@ -7231,7 +7237,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="172" spans="2:9">
+    <row r="172" spans="2:9" hidden="1">
       <c r="B172" t="s">
         <v>11</v>
       </c>
@@ -7435,7 +7441,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="181" spans="2:9">
+    <row r="181" spans="2:9" hidden="1">
       <c r="B181" t="s">
         <v>11</v>
       </c>
@@ -7455,7 +7461,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="182" spans="2:9">
+    <row r="182" spans="2:9" hidden="1">
       <c r="B182" t="s">
         <v>11</v>
       </c>
@@ -7475,7 +7481,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="183" spans="2:9">
+    <row r="183" spans="2:9" hidden="1">
       <c r="B183" t="s">
         <v>11</v>
       </c>
@@ -7495,7 +7501,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="184" spans="2:9">
+    <row r="184" spans="2:9" hidden="1">
       <c r="B184" t="s">
         <v>11</v>
       </c>
@@ -7518,7 +7524,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="185" spans="2:9">
+    <row r="185" spans="2:9" hidden="1">
       <c r="B185" t="s">
         <v>11</v>
       </c>
@@ -7541,7 +7547,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="186" spans="2:9">
+    <row r="186" spans="2:9" hidden="1">
       <c r="B186" t="s">
         <v>11</v>
       </c>
@@ -7561,7 +7567,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="187" spans="2:9">
+    <row r="187" spans="2:9" hidden="1">
       <c r="B187" t="s">
         <v>11</v>
       </c>
@@ -7581,7 +7587,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="188" spans="2:9">
+    <row r="188" spans="2:9" hidden="1">
       <c r="B188" t="s">
         <v>11</v>
       </c>
@@ -7601,7 +7607,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="189" spans="2:9">
+    <row r="189" spans="2:9" hidden="1">
       <c r="B189" t="s">
         <v>11</v>
       </c>
@@ -7621,7 +7627,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="190" spans="2:9">
+    <row r="190" spans="2:9" hidden="1">
       <c r="B190" t="s">
         <v>11</v>
       </c>
@@ -7641,7 +7647,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="191" spans="2:9">
+    <row r="191" spans="2:9" hidden="1">
       <c r="B191" t="s">
         <v>11</v>
       </c>
@@ -7661,7 +7667,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="192" spans="2:9">
+    <row r="192" spans="2:9" hidden="1">
       <c r="B192" t="s">
         <v>11</v>
       </c>
@@ -7681,7 +7687,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="193" spans="2:8">
+    <row r="193" spans="2:8" hidden="1">
       <c r="B193" t="s">
         <v>11</v>
       </c>
@@ -7701,7 +7707,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="194" spans="2:8">
+    <row r="194" spans="2:8" hidden="1">
       <c r="B194" t="s">
         <v>11</v>
       </c>
@@ -7721,7 +7727,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="195" spans="2:8">
+    <row r="195" spans="2:8" hidden="1">
       <c r="B195" t="s">
         <v>11</v>
       </c>
@@ -7741,7 +7747,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="196" spans="2:8">
+    <row r="196" spans="2:8" hidden="1">
       <c r="B196" t="s">
         <v>11</v>
       </c>
@@ -7761,7 +7767,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="197" spans="2:8">
+    <row r="197" spans="2:8" hidden="1">
       <c r="B197" t="s">
         <v>11</v>
       </c>
@@ -7781,7 +7787,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="198" spans="2:8">
+    <row r="198" spans="2:8" hidden="1">
       <c r="B198" t="s">
         <v>11</v>
       </c>
@@ -7801,7 +7807,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="199" spans="2:8">
+    <row r="199" spans="2:8" hidden="1">
       <c r="B199" t="s">
         <v>11</v>
       </c>
@@ -7821,7 +7827,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="200" spans="2:8">
+    <row r="200" spans="2:8" hidden="1">
       <c r="B200" t="s">
         <v>11</v>
       </c>
@@ -7841,7 +7847,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="201" spans="2:8">
+    <row r="201" spans="2:8" hidden="1">
       <c r="B201" t="s">
         <v>11</v>
       </c>
@@ -7861,7 +7867,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="202" spans="2:8">
+    <row r="202" spans="2:8" hidden="1">
       <c r="B202" t="s">
         <v>11</v>
       </c>
@@ -7881,7 +7887,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="203" spans="2:8">
+    <row r="203" spans="2:8" hidden="1">
       <c r="B203" t="s">
         <v>11</v>
       </c>
@@ -7901,7 +7907,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="204" spans="2:8">
+    <row r="204" spans="2:8" hidden="1">
       <c r="B204" t="s">
         <v>11</v>
       </c>
@@ -7921,7 +7927,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="205" spans="2:8">
+    <row r="205" spans="2:8" hidden="1">
       <c r="B205" t="s">
         <v>11</v>
       </c>
@@ -7941,7 +7947,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="206" spans="2:8">
+    <row r="206" spans="2:8" hidden="1">
       <c r="B206" t="s">
         <v>11</v>
       </c>
@@ -7961,7 +7967,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="207" spans="2:8">
+    <row r="207" spans="2:8" hidden="1">
       <c r="B207" t="s">
         <v>11</v>
       </c>
@@ -7981,7 +7987,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="208" spans="2:8">
+    <row r="208" spans="2:8" hidden="1">
       <c r="B208" t="s">
         <v>11</v>
       </c>
@@ -8001,7 +8007,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="209" spans="2:9">
+    <row r="209" spans="2:9" hidden="1">
       <c r="B209" t="s">
         <v>11</v>
       </c>
@@ -8021,7 +8027,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="210" spans="2:9">
+    <row r="210" spans="2:9" hidden="1">
       <c r="B210" t="s">
         <v>11</v>
       </c>
@@ -8041,7 +8047,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="211" spans="2:9">
+    <row r="211" spans="2:9" hidden="1">
       <c r="B211" t="s">
         <v>11</v>
       </c>
@@ -8061,7 +8067,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="212" spans="2:9">
+    <row r="212" spans="2:9" hidden="1">
       <c r="B212" t="s">
         <v>11</v>
       </c>
@@ -8081,7 +8087,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="213" spans="2:9">
+    <row r="213" spans="2:9" hidden="1">
       <c r="B213" t="s">
         <v>11</v>
       </c>
@@ -8101,7 +8107,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="214" spans="2:9">
+    <row r="214" spans="2:9" hidden="1">
       <c r="B214" t="s">
         <v>11</v>
       </c>
@@ -8121,7 +8127,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="215" spans="2:9">
+    <row r="215" spans="2:9" hidden="1">
       <c r="B215" t="s">
         <v>11</v>
       </c>
@@ -8141,7 +8147,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="216" spans="2:9">
+    <row r="216" spans="2:9" hidden="1">
       <c r="B216" t="s">
         <v>11</v>
       </c>
@@ -8161,7 +8167,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="217" spans="2:9">
+    <row r="217" spans="2:9" hidden="1">
       <c r="B217" t="s">
         <v>11</v>
       </c>
@@ -8181,7 +8187,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="218" spans="2:9">
+    <row r="218" spans="2:9" hidden="1">
       <c r="B218" t="s">
         <v>11</v>
       </c>
@@ -8201,7 +8207,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="219" spans="2:9">
+    <row r="219" spans="2:9" hidden="1">
       <c r="B219" t="s">
         <v>11</v>
       </c>
@@ -8221,7 +8227,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="220" spans="2:9">
+    <row r="220" spans="2:9" hidden="1">
       <c r="B220" t="s">
         <v>11</v>
       </c>
@@ -8241,7 +8247,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="221" spans="2:9">
+    <row r="221" spans="2:9" hidden="1">
       <c r="B221" t="s">
         <v>11</v>
       </c>
@@ -8261,7 +8267,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="222" spans="2:9">
+    <row r="222" spans="2:9" hidden="1">
       <c r="B222" t="s">
         <v>11</v>
       </c>
@@ -8281,7 +8287,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="223" spans="2:9">
+    <row r="223" spans="2:9" hidden="1">
       <c r="B223" t="s">
         <v>11</v>
       </c>
@@ -8301,7 +8307,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="224" spans="2:9">
+    <row r="224" spans="2:9" hidden="1">
       <c r="B224" t="s">
         <v>11</v>
       </c>
@@ -8324,7 +8330,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="225" spans="2:9">
+    <row r="225" spans="2:9" hidden="1">
       <c r="B225" t="s">
         <v>11</v>
       </c>
@@ -8347,7 +8353,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="226" spans="2:9">
+    <row r="226" spans="2:9" hidden="1">
       <c r="B226" t="s">
         <v>11</v>
       </c>
@@ -8370,7 +8376,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="227" spans="2:9">
+    <row r="227" spans="2:9" hidden="1">
       <c r="B227" t="s">
         <v>11</v>
       </c>
@@ -8393,7 +8399,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="228" spans="2:9">
+    <row r="228" spans="2:9" hidden="1">
       <c r="B228" t="s">
         <v>11</v>
       </c>
@@ -8416,7 +8422,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="229" spans="2:9">
+    <row r="229" spans="2:9" hidden="1">
       <c r="B229" t="s">
         <v>11</v>
       </c>
@@ -8436,7 +8442,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="230" spans="2:9">
+    <row r="230" spans="2:9" hidden="1">
       <c r="B230" t="s">
         <v>11</v>
       </c>
@@ -8456,7 +8462,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="231" spans="2:9">
+    <row r="231" spans="2:9" hidden="1">
       <c r="B231" t="s">
         <v>11</v>
       </c>
@@ -8476,7 +8482,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="232" spans="2:9">
+    <row r="232" spans="2:9" hidden="1">
       <c r="B232" t="s">
         <v>11</v>
       </c>
@@ -8496,7 +8502,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="233" spans="2:9">
+    <row r="233" spans="2:9" hidden="1">
       <c r="B233" t="s">
         <v>11</v>
       </c>
@@ -8516,7 +8522,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="234" spans="2:9">
+    <row r="234" spans="2:9" hidden="1">
       <c r="B234" t="s">
         <v>11</v>
       </c>
@@ -8536,7 +8542,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="235" spans="2:9">
+    <row r="235" spans="2:9" hidden="1">
       <c r="B235" t="s">
         <v>11</v>
       </c>
@@ -8556,7 +8562,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="236" spans="2:9">
+    <row r="236" spans="2:9" hidden="1">
       <c r="B236" t="s">
         <v>11</v>
       </c>
@@ -8576,7 +8582,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="237" spans="2:9">
+    <row r="237" spans="2:9" hidden="1">
       <c r="B237" t="s">
         <v>11</v>
       </c>
@@ -8596,7 +8602,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="238" spans="2:9">
+    <row r="238" spans="2:9" hidden="1">
       <c r="B238" t="s">
         <v>11</v>
       </c>
@@ -8616,7 +8622,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="239" spans="2:9">
+    <row r="239" spans="2:9" hidden="1">
       <c r="B239" t="s">
         <v>11</v>
       </c>
@@ -8636,7 +8642,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="240" spans="2:9">
+    <row r="240" spans="2:9" hidden="1">
       <c r="B240" t="s">
         <v>11</v>
       </c>
@@ -8656,7 +8662,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="241" spans="2:8">
+    <row r="241" spans="2:8" hidden="1">
       <c r="B241" t="s">
         <v>11</v>
       </c>
@@ -8676,7 +8682,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="242" spans="2:8">
+    <row r="242" spans="2:8" hidden="1">
       <c r="B242" t="s">
         <v>11</v>
       </c>
@@ -8696,7 +8702,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="243" spans="2:8">
+    <row r="243" spans="2:8" hidden="1">
       <c r="B243" t="s">
         <v>11</v>
       </c>
@@ -8796,7 +8802,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="248" spans="2:8">
+    <row r="248" spans="2:8" hidden="1">
       <c r="B248" t="s">
         <v>11</v>
       </c>
@@ -8816,7 +8822,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="249" spans="2:8">
+    <row r="249" spans="2:8" hidden="1">
       <c r="B249" t="s">
         <v>11</v>
       </c>
@@ -8836,7 +8842,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="250" spans="2:8">
+    <row r="250" spans="2:8" hidden="1">
       <c r="B250" t="s">
         <v>11</v>
       </c>
@@ -8856,7 +8862,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="251" spans="2:8">
+    <row r="251" spans="2:8" hidden="1">
       <c r="B251" t="s">
         <v>11</v>
       </c>
@@ -8876,7 +8882,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="252" spans="2:8">
+    <row r="252" spans="2:8" hidden="1">
       <c r="B252" t="s">
         <v>11</v>
       </c>
@@ -8896,7 +8902,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="253" spans="2:8">
+    <row r="253" spans="2:8" hidden="1">
       <c r="B253" t="s">
         <v>11</v>
       </c>
@@ -8916,7 +8922,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="254" spans="2:8">
+    <row r="254" spans="2:8" hidden="1">
       <c r="B254" t="s">
         <v>11</v>
       </c>
@@ -8956,7 +8962,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="256" spans="2:8">
+    <row r="256" spans="2:8" hidden="1">
       <c r="B256" t="s">
         <v>11</v>
       </c>
@@ -8996,7 +9002,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="258" spans="2:8">
+    <row r="258" spans="2:8" hidden="1">
       <c r="B258" t="s">
         <v>11</v>
       </c>
@@ -9016,7 +9022,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="259" spans="2:8">
+    <row r="259" spans="2:8" hidden="1">
       <c r="B259" t="s">
         <v>11</v>
       </c>
@@ -9036,7 +9042,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="260" spans="2:8">
+    <row r="260" spans="2:8" hidden="1">
       <c r="B260" t="s">
         <v>11</v>
       </c>
@@ -9056,7 +9062,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="261" spans="2:8">
+    <row r="261" spans="2:8" hidden="1">
       <c r="B261" t="s">
         <v>11</v>
       </c>
@@ -9076,7 +9082,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="262" spans="2:8">
+    <row r="262" spans="2:8" hidden="1">
       <c r="B262" t="s">
         <v>11</v>
       </c>
@@ -9096,7 +9102,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="263" spans="2:8">
+    <row r="263" spans="2:8" hidden="1">
       <c r="B263" t="s">
         <v>11</v>
       </c>
@@ -9116,7 +9122,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="264" spans="2:8">
+    <row r="264" spans="2:8" hidden="1">
       <c r="B264" t="s">
         <v>11</v>
       </c>
@@ -9136,7 +9142,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="265" spans="2:8">
+    <row r="265" spans="2:8" hidden="1">
       <c r="B265" t="s">
         <v>11</v>
       </c>
@@ -9156,7 +9162,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="266" spans="2:8">
+    <row r="266" spans="2:8" hidden="1">
       <c r="B266" t="s">
         <v>11</v>
       </c>
@@ -9176,7 +9182,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="267" spans="2:8">
+    <row r="267" spans="2:8" hidden="1">
       <c r="B267" t="s">
         <v>11</v>
       </c>
@@ -9196,7 +9202,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="268" spans="2:8">
+    <row r="268" spans="2:8" hidden="1">
       <c r="B268" t="s">
         <v>11</v>
       </c>
@@ -9216,7 +9222,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="269" spans="2:8">
+    <row r="269" spans="2:8" hidden="1">
       <c r="B269" t="s">
         <v>11</v>
       </c>
@@ -9236,7 +9242,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="270" spans="2:8">
+    <row r="270" spans="2:8" hidden="1">
       <c r="B270" t="s">
         <v>11</v>
       </c>
@@ -9256,7 +9262,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="271" spans="2:8">
+    <row r="271" spans="2:8" hidden="1">
       <c r="B271" t="s">
         <v>11</v>
       </c>
@@ -9276,7 +9282,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="272" spans="2:8">
+    <row r="272" spans="2:8" hidden="1">
       <c r="B272" t="s">
         <v>11</v>
       </c>
@@ -9296,7 +9302,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="273" spans="2:8">
+    <row r="273" spans="2:8" hidden="1">
       <c r="B273" t="s">
         <v>11</v>
       </c>
@@ -9316,7 +9322,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="274" spans="2:8">
+    <row r="274" spans="2:8" hidden="1">
       <c r="B274" t="s">
         <v>11</v>
       </c>
@@ -9336,7 +9342,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="275" spans="2:8">
+    <row r="275" spans="2:8" hidden="1">
       <c r="B275" t="s">
         <v>11</v>
       </c>
@@ -9356,7 +9362,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="276" spans="2:8">
+    <row r="276" spans="2:8" hidden="1">
       <c r="B276" t="s">
         <v>11</v>
       </c>
@@ -9376,7 +9382,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="277" spans="2:8">
+    <row r="277" spans="2:8" hidden="1">
       <c r="B277" t="s">
         <v>11</v>
       </c>
@@ -9396,7 +9402,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="278" spans="2:8">
+    <row r="278" spans="2:8" hidden="1">
       <c r="B278" t="s">
         <v>11</v>
       </c>
@@ -9416,7 +9422,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="279" spans="2:8">
+    <row r="279" spans="2:8" hidden="1">
       <c r="B279" t="s">
         <v>11</v>
       </c>
@@ -9436,7 +9442,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="280" spans="2:8">
+    <row r="280" spans="2:8" hidden="1">
       <c r="B280" t="s">
         <v>11</v>
       </c>
@@ -9456,7 +9462,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="281" spans="2:8">
+    <row r="281" spans="2:8" hidden="1">
       <c r="B281" t="s">
         <v>11</v>
       </c>
@@ -9696,7 +9702,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="293" spans="2:9">
+    <row r="293" spans="2:9" hidden="1">
       <c r="B293" t="s">
         <v>11</v>
       </c>
@@ -9716,7 +9722,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="294" spans="2:9">
+    <row r="294" spans="2:9" hidden="1">
       <c r="B294" t="s">
         <v>11</v>
       </c>
@@ -9736,7 +9742,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="295" spans="2:9">
+    <row r="295" spans="2:9" hidden="1">
       <c r="B295" t="s">
         <v>11</v>
       </c>
@@ -9756,7 +9762,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="296" spans="2:9">
+    <row r="296" spans="2:9" hidden="1">
       <c r="B296" t="s">
         <v>11</v>
       </c>
@@ -9779,7 +9785,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="297" spans="2:9">
+    <row r="297" spans="2:9" hidden="1">
       <c r="B297" t="s">
         <v>11</v>
       </c>
@@ -9802,7 +9808,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="298" spans="2:9">
+    <row r="298" spans="2:9" hidden="1">
       <c r="B298" t="s">
         <v>11</v>
       </c>
@@ -9825,7 +9831,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="299" spans="2:9">
+    <row r="299" spans="2:9" hidden="1">
       <c r="B299" t="s">
         <v>11</v>
       </c>
@@ -9848,7 +9854,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="300" spans="2:9">
+    <row r="300" spans="2:9" hidden="1">
       <c r="B300" t="s">
         <v>11</v>
       </c>
@@ -9871,7 +9877,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="301" spans="2:9">
+    <row r="301" spans="2:9" hidden="1">
       <c r="B301" t="s">
         <v>11</v>
       </c>
@@ -9894,7 +9900,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="302" spans="2:9">
+    <row r="302" spans="2:9" hidden="1">
       <c r="B302" t="s">
         <v>11</v>
       </c>
@@ -9917,7 +9923,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="303" spans="2:9">
+    <row r="303" spans="2:9" hidden="1">
       <c r="B303" t="s">
         <v>11</v>
       </c>
@@ -9940,7 +9946,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="304" spans="2:9">
+    <row r="304" spans="2:9" hidden="1">
       <c r="B304" t="s">
         <v>11</v>
       </c>
@@ -9963,7 +9969,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="305" spans="2:9">
+    <row r="305" spans="2:9" hidden="1">
       <c r="B305" t="s">
         <v>11</v>
       </c>
@@ -9986,7 +9992,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="306" spans="2:9">
+    <row r="306" spans="2:9" hidden="1">
       <c r="B306" t="s">
         <v>11</v>
       </c>
@@ -10009,7 +10015,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="307" spans="2:9">
+    <row r="307" spans="2:9" hidden="1">
       <c r="B307" t="s">
         <v>11</v>
       </c>
@@ -10032,7 +10038,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="308" spans="2:9">
+    <row r="308" spans="2:9" hidden="1">
       <c r="B308" t="s">
         <v>11</v>
       </c>
@@ -10055,7 +10061,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="309" spans="2:9">
+    <row r="309" spans="2:9" hidden="1">
       <c r="B309" t="s">
         <v>11</v>
       </c>
@@ -10078,7 +10084,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="310" spans="2:9">
+    <row r="310" spans="2:9" hidden="1">
       <c r="B310" t="s">
         <v>11</v>
       </c>
@@ -10101,7 +10107,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="311" spans="2:9">
+    <row r="311" spans="2:9" hidden="1">
       <c r="B311" t="s">
         <v>11</v>
       </c>
@@ -10124,7 +10130,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="312" spans="2:9">
+    <row r="312" spans="2:9" hidden="1">
       <c r="B312" t="s">
         <v>11</v>
       </c>
@@ -10147,7 +10153,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="313" spans="2:9">
+    <row r="313" spans="2:9" hidden="1">
       <c r="B313" t="s">
         <v>11</v>
       </c>
@@ -10170,7 +10176,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="314" spans="2:9">
+    <row r="314" spans="2:9" hidden="1">
       <c r="B314" t="s">
         <v>11</v>
       </c>
@@ -10193,7 +10199,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="315" spans="2:9">
+    <row r="315" spans="2:9" hidden="1">
       <c r="B315" t="s">
         <v>11</v>
       </c>
@@ -10216,7 +10222,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="316" spans="2:9">
+    <row r="316" spans="2:9" hidden="1">
       <c r="B316" t="s">
         <v>11</v>
       </c>
@@ -10239,7 +10245,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="317" spans="2:9">
+    <row r="317" spans="2:9" hidden="1">
       <c r="B317" t="s">
         <v>11</v>
       </c>
@@ -10446,7 +10452,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="326" spans="2:9">
+    <row r="326" spans="2:9" hidden="1">
       <c r="B326" t="s">
         <v>11</v>
       </c>
@@ -10630,7 +10636,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="334" spans="2:9">
+    <row r="334" spans="2:9" hidden="1">
       <c r="B334" t="s">
         <v>11</v>
       </c>
@@ -10653,7 +10659,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="335" spans="2:9">
+    <row r="335" spans="2:9" hidden="1">
       <c r="B335" t="s">
         <v>11</v>
       </c>
@@ -10673,7 +10679,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="336" spans="2:9">
+    <row r="336" spans="2:9" hidden="1">
       <c r="B336" t="s">
         <v>11</v>
       </c>
@@ -10693,7 +10699,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="337" spans="2:9">
+    <row r="337" spans="2:9" hidden="1">
       <c r="B337" t="s">
         <v>11</v>
       </c>
@@ -10713,7 +10719,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="338" spans="2:9">
+    <row r="338" spans="2:9" hidden="1">
       <c r="B338" t="s">
         <v>11</v>
       </c>
@@ -10733,7 +10739,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="339" spans="2:9">
+    <row r="339" spans="2:9" hidden="1">
       <c r="B339" t="s">
         <v>11</v>
       </c>
@@ -10753,7 +10759,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="340" spans="2:9">
+    <row r="340" spans="2:9" hidden="1">
       <c r="B340" t="s">
         <v>11</v>
       </c>
@@ -10773,7 +10779,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="341" spans="2:9">
+    <row r="341" spans="2:9" hidden="1">
       <c r="B341" t="s">
         <v>11</v>
       </c>
@@ -10793,7 +10799,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="342" spans="2:9">
+    <row r="342" spans="2:9" hidden="1">
       <c r="B342" t="s">
         <v>11</v>
       </c>
@@ -10813,7 +10819,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="343" spans="2:9">
+    <row r="343" spans="2:9" hidden="1">
       <c r="B343" t="s">
         <v>11</v>
       </c>
@@ -10833,7 +10839,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="344" spans="2:9">
+    <row r="344" spans="2:9" hidden="1">
       <c r="B344" t="s">
         <v>11</v>
       </c>
@@ -10853,7 +10859,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="345" spans="2:9">
+    <row r="345" spans="2:9" hidden="1">
       <c r="B345" t="s">
         <v>11</v>
       </c>
@@ -10873,7 +10879,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="346" spans="2:9">
+    <row r="346" spans="2:9" hidden="1">
       <c r="B346" t="s">
         <v>11</v>
       </c>
@@ -10893,7 +10899,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="347" spans="2:9">
+    <row r="347" spans="2:9" hidden="1">
       <c r="B347" t="s">
         <v>11</v>
       </c>
@@ -10913,7 +10919,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="348" spans="2:9">
+    <row r="348" spans="2:9" hidden="1">
       <c r="B348" t="s">
         <v>11</v>
       </c>
@@ -10933,7 +10939,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="2:9">
+    <row r="349" spans="2:9" hidden="1">
       <c r="B349" t="s">
         <v>11</v>
       </c>
@@ -10956,7 +10962,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="350" spans="2:9">
+    <row r="350" spans="2:9" hidden="1">
       <c r="B350" t="s">
         <v>11</v>
       </c>
@@ -10979,7 +10985,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="351" spans="2:9">
+    <row r="351" spans="2:9" hidden="1">
       <c r="B351" t="s">
         <v>11</v>
       </c>
@@ -11002,7 +11008,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="352" spans="2:9">
+    <row r="352" spans="2:9" hidden="1">
       <c r="B352" t="s">
         <v>11</v>
       </c>
@@ -11025,7 +11031,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="353" spans="2:9">
+    <row r="353" spans="2:9" hidden="1">
       <c r="B353" t="s">
         <v>11</v>
       </c>
@@ -11048,7 +11054,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="354" spans="2:9">
+    <row r="354" spans="2:9" hidden="1">
       <c r="B354" t="s">
         <v>11</v>
       </c>
@@ -11071,7 +11077,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="355" spans="2:9">
+    <row r="355" spans="2:9" hidden="1">
       <c r="B355" t="s">
         <v>11</v>
       </c>
@@ -11094,7 +11100,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="356" spans="2:9">
+    <row r="356" spans="2:9" hidden="1">
       <c r="B356" t="s">
         <v>11</v>
       </c>
@@ -11117,7 +11123,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="357" spans="2:9">
+    <row r="357" spans="2:9" hidden="1">
       <c r="B357" t="s">
         <v>11</v>
       </c>
@@ -11137,7 +11143,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="358" spans="2:9">
+    <row r="358" spans="2:9" hidden="1">
       <c r="B358" t="s">
         <v>11</v>
       </c>
@@ -11157,7 +11163,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="359" spans="2:9">
+    <row r="359" spans="2:9" hidden="1">
       <c r="B359" t="s">
         <v>11</v>
       </c>
@@ -11177,7 +11183,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="360" spans="2:9">
+    <row r="360" spans="2:9" hidden="1">
       <c r="B360" t="s">
         <v>11</v>
       </c>
@@ -11197,7 +11203,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="361" spans="2:9">
+    <row r="361" spans="2:9" hidden="1">
       <c r="B361" t="s">
         <v>11</v>
       </c>
@@ -11220,7 +11226,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="362" spans="2:9">
+    <row r="362" spans="2:9" hidden="1">
       <c r="B362" t="s">
         <v>11</v>
       </c>
@@ -11243,7 +11249,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="363" spans="2:9">
+    <row r="363" spans="2:9" hidden="1">
       <c r="B363" t="s">
         <v>11</v>
       </c>
@@ -11266,7 +11272,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="364" spans="2:9">
+    <row r="364" spans="2:9" hidden="1">
       <c r="B364" t="s">
         <v>11</v>
       </c>
@@ -11289,7 +11295,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="365" spans="2:9">
+    <row r="365" spans="2:9" hidden="1">
       <c r="B365" t="s">
         <v>11</v>
       </c>
@@ -11309,7 +11315,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="366" spans="2:9">
+    <row r="366" spans="2:9" hidden="1">
       <c r="B366" t="s">
         <v>11</v>
       </c>
@@ -11332,7 +11338,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="367" spans="2:9">
+    <row r="367" spans="2:9" hidden="1">
       <c r="B367" t="s">
         <v>11</v>
       </c>
@@ -11352,7 +11358,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="368" spans="2:9">
+    <row r="368" spans="2:9" hidden="1">
       <c r="B368" t="s">
         <v>11</v>
       </c>
@@ -11375,7 +11381,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="369" spans="2:9">
+    <row r="369" spans="2:9" hidden="1">
       <c r="B369" t="s">
         <v>11</v>
       </c>
@@ -11398,7 +11404,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="370" spans="2:9">
+    <row r="370" spans="2:9" hidden="1">
       <c r="B370" t="s">
         <v>11</v>
       </c>
@@ -11421,7 +11427,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="371" spans="2:9">
+    <row r="371" spans="2:9" hidden="1">
       <c r="B371" t="s">
         <v>11</v>
       </c>
@@ -11444,7 +11450,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="372" spans="2:9">
+    <row r="372" spans="2:9" hidden="1">
       <c r="B372" t="s">
         <v>11</v>
       </c>
@@ -11467,7 +11473,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="373" spans="2:9">
+    <row r="373" spans="2:9" hidden="1">
       <c r="B373" t="s">
         <v>11</v>
       </c>
@@ -11490,7 +11496,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="374" spans="2:9">
+    <row r="374" spans="2:9" hidden="1">
       <c r="B374" t="s">
         <v>11</v>
       </c>
@@ -11513,7 +11519,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="375" spans="2:9">
+    <row r="375" spans="2:9" hidden="1">
       <c r="B375" t="s">
         <v>11</v>
       </c>
@@ -11536,7 +11542,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="376" spans="2:9">
+    <row r="376" spans="2:9" hidden="1">
       <c r="B376" t="s">
         <v>11</v>
       </c>
@@ -11559,7 +11565,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="377" spans="2:9">
+    <row r="377" spans="2:9" hidden="1">
       <c r="B377" t="s">
         <v>11</v>
       </c>
@@ -11582,7 +11588,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="378" spans="2:9">
+    <row r="378" spans="2:9" hidden="1">
       <c r="B378" t="s">
         <v>11</v>
       </c>
@@ -11605,7 +11611,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="379" spans="2:9">
+    <row r="379" spans="2:9" hidden="1">
       <c r="B379" t="s">
         <v>11</v>
       </c>
@@ -11628,7 +11634,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="380" spans="2:9">
+    <row r="380" spans="2:9" hidden="1">
       <c r="B380" t="s">
         <v>11</v>
       </c>
@@ -11651,7 +11657,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="381" spans="2:9">
+    <row r="381" spans="2:9" hidden="1">
       <c r="B381" t="s">
         <v>11</v>
       </c>
@@ -11674,7 +11680,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="382" spans="2:9">
+    <row r="382" spans="2:9" hidden="1">
       <c r="B382" t="s">
         <v>11</v>
       </c>
@@ -11697,7 +11703,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="383" spans="2:9">
+    <row r="383" spans="2:9" hidden="1">
       <c r="B383" t="s">
         <v>11</v>
       </c>
@@ -11717,7 +11723,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="384" spans="2:9">
+    <row r="384" spans="2:9" hidden="1">
       <c r="B384" t="s">
         <v>11</v>
       </c>
@@ -11740,7 +11746,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="385" spans="2:9">
+    <row r="385" spans="2:9" hidden="1">
       <c r="B385" t="s">
         <v>11</v>
       </c>
@@ -11763,7 +11769,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="386" spans="2:9">
+    <row r="386" spans="2:9" hidden="1">
       <c r="B386" t="s">
         <v>11</v>
       </c>
@@ -11786,7 +11792,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="387" spans="2:9">
+    <row r="387" spans="2:9" hidden="1">
       <c r="B387" t="s">
         <v>11</v>
       </c>
@@ -11809,7 +11815,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="388" spans="2:9">
+    <row r="388" spans="2:9" hidden="1">
       <c r="B388" t="s">
         <v>11</v>
       </c>
@@ -11832,7 +11838,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="389" spans="2:9">
+    <row r="389" spans="2:9" hidden="1">
       <c r="B389" t="s">
         <v>11</v>
       </c>
@@ -11855,7 +11861,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="390" spans="2:9">
+    <row r="390" spans="2:9" hidden="1">
       <c r="B390" t="s">
         <v>11</v>
       </c>
@@ -11878,7 +11884,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="391" spans="2:9">
+    <row r="391" spans="2:9" hidden="1">
       <c r="B391" t="s">
         <v>11</v>
       </c>
@@ -11901,7 +11907,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="392" spans="2:9">
+    <row r="392" spans="2:9" hidden="1">
       <c r="B392" t="s">
         <v>11</v>
       </c>
@@ -11924,7 +11930,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="393" spans="2:9">
+    <row r="393" spans="2:9" hidden="1">
       <c r="B393" t="s">
         <v>11</v>
       </c>
@@ -11944,7 +11950,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="394" spans="2:9">
+    <row r="394" spans="2:9" hidden="1">
       <c r="B394" t="s">
         <v>11</v>
       </c>
@@ -11964,7 +11970,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="395" spans="2:9">
+    <row r="395" spans="2:9" hidden="1">
       <c r="B395" t="s">
         <v>11</v>
       </c>
@@ -11987,7 +11993,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="396" spans="2:9">
+    <row r="396" spans="2:9" hidden="1">
       <c r="B396" t="s">
         <v>11</v>
       </c>
@@ -12010,7 +12016,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="397" spans="2:9">
+    <row r="397" spans="2:9" hidden="1">
       <c r="B397" t="s">
         <v>11</v>
       </c>
@@ -12030,7 +12036,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="398" spans="2:9">
+    <row r="398" spans="2:9" hidden="1">
       <c r="B398" t="s">
         <v>11</v>
       </c>
@@ -12050,7 +12056,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="399" spans="2:9">
+    <row r="399" spans="2:9" hidden="1">
       <c r="B399" t="s">
         <v>11</v>
       </c>
@@ -12070,7 +12076,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="400" spans="2:9">
+    <row r="400" spans="2:9" hidden="1">
       <c r="B400" t="s">
         <v>11</v>
       </c>
@@ -12090,7 +12096,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="401" spans="2:8">
+    <row r="401" spans="2:8" hidden="1">
       <c r="B401" t="s">
         <v>11</v>
       </c>
@@ -12110,7 +12116,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="402" spans="2:8">
+    <row r="402" spans="2:8" hidden="1">
       <c r="B402" t="s">
         <v>11</v>
       </c>
@@ -12130,7 +12136,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="403" spans="2:8">
+    <row r="403" spans="2:8" hidden="1">
       <c r="B403" t="s">
         <v>11</v>
       </c>
@@ -12150,7 +12156,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="404" spans="2:8">
+    <row r="404" spans="2:8" hidden="1">
       <c r="B404" t="s">
         <v>11</v>
       </c>
@@ -12390,7 +12396,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="416" spans="2:8">
+    <row r="416" spans="2:8" hidden="1">
       <c r="B416" t="s">
         <v>11</v>
       </c>
@@ -12410,7 +12416,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="417" spans="2:8">
+    <row r="417" spans="2:8" hidden="1">
       <c r="B417" t="s">
         <v>11</v>
       </c>
@@ -12430,7 +12436,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="418" spans="2:8">
+    <row r="418" spans="2:8" hidden="1">
       <c r="B418" t="s">
         <v>11</v>
       </c>
@@ -12450,7 +12456,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="419" spans="2:8">
+    <row r="419" spans="2:8" hidden="1">
       <c r="B419" t="s">
         <v>11</v>
       </c>
@@ -12470,7 +12476,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="420" spans="2:8">
+    <row r="420" spans="2:8" hidden="1">
       <c r="B420" t="s">
         <v>11</v>
       </c>
@@ -12710,7 +12716,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="432" spans="2:8">
+    <row r="432" spans="2:8" hidden="1">
       <c r="B432" t="s">
         <v>11</v>
       </c>
@@ -12730,7 +12736,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="433" spans="2:9">
+    <row r="433" spans="2:9" hidden="1">
       <c r="B433" t="s">
         <v>11</v>
       </c>
@@ -12750,7 +12756,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="434" spans="2:9">
+    <row r="434" spans="2:9" hidden="1">
       <c r="B434" t="s">
         <v>11</v>
       </c>
@@ -12770,7 +12776,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="435" spans="2:9">
+    <row r="435" spans="2:9" hidden="1">
       <c r="B435" t="s">
         <v>11</v>
       </c>
@@ -12790,7 +12796,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="436" spans="2:9">
+    <row r="436" spans="2:9" hidden="1">
       <c r="B436" t="s">
         <v>11</v>
       </c>
@@ -12850,7 +12856,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="439" spans="2:9">
+    <row r="439" spans="2:9" hidden="1">
       <c r="B439" t="s">
         <v>11</v>
       </c>
@@ -12870,7 +12876,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="440" spans="2:9">
+    <row r="440" spans="2:9" hidden="1">
       <c r="B440" t="s">
         <v>11</v>
       </c>
@@ -12893,7 +12899,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="441" spans="2:9">
+    <row r="441" spans="2:9" hidden="1">
       <c r="B441" t="s">
         <v>11</v>
       </c>
@@ -12916,7 +12922,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="442" spans="2:9">
+    <row r="442" spans="2:9" hidden="1">
       <c r="B442" t="s">
         <v>11</v>
       </c>
@@ -12939,7 +12945,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="443" spans="2:9">
+    <row r="443" spans="2:9" hidden="1">
       <c r="B443" t="s">
         <v>11</v>
       </c>
@@ -12962,7 +12968,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="444" spans="2:9">
+    <row r="444" spans="2:9" hidden="1">
       <c r="B444" t="s">
         <v>11</v>
       </c>
@@ -12985,7 +12991,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="445" spans="2:9">
+    <row r="445" spans="2:9" hidden="1">
       <c r="B445" t="s">
         <v>11</v>
       </c>
@@ -13005,7 +13011,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="446" spans="2:9">
+    <row r="446" spans="2:9" hidden="1">
       <c r="B446" t="s">
         <v>11</v>
       </c>
@@ -13028,7 +13034,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="447" spans="2:9">
+    <row r="447" spans="2:9" hidden="1">
       <c r="B447" t="s">
         <v>11</v>
       </c>
@@ -13051,7 +13057,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="448" spans="2:9">
+    <row r="448" spans="2:9" hidden="1">
       <c r="B448" t="s">
         <v>11</v>
       </c>
@@ -13071,7 +13077,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="449" spans="2:9">
+    <row r="449" spans="2:9" hidden="1">
       <c r="B449" t="s">
         <v>11</v>
       </c>
@@ -13094,7 +13100,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="450" spans="2:9">
+    <row r="450" spans="2:9" hidden="1">
       <c r="B450" t="s">
         <v>11</v>
       </c>
@@ -13117,7 +13123,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="451" spans="2:9">
+    <row r="451" spans="2:9" hidden="1">
       <c r="B451" t="s">
         <v>11</v>
       </c>
@@ -13140,7 +13146,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="452" spans="2:9">
+    <row r="452" spans="2:9" hidden="1">
       <c r="B452" t="s">
         <v>11</v>
       </c>
@@ -13163,7 +13169,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="453" spans="2:9">
+    <row r="453" spans="2:9" hidden="1">
       <c r="B453" t="s">
         <v>11</v>
       </c>
@@ -13186,7 +13192,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="454" spans="2:9">
+    <row r="454" spans="2:9" hidden="1">
       <c r="B454" t="s">
         <v>11</v>
       </c>
@@ -13209,7 +13215,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="455" spans="2:9">
+    <row r="455" spans="2:9" hidden="1">
       <c r="B455" t="s">
         <v>11</v>
       </c>
@@ -13232,7 +13238,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="456" spans="2:9">
+    <row r="456" spans="2:9" hidden="1">
       <c r="B456" t="s">
         <v>11</v>
       </c>
@@ -13255,7 +13261,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="457" spans="2:9">
+    <row r="457" spans="2:9" hidden="1">
       <c r="B457" t="s">
         <v>11</v>
       </c>
@@ -13278,7 +13284,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="458" spans="2:9">
+    <row r="458" spans="2:9" hidden="1">
       <c r="B458" t="s">
         <v>11</v>
       </c>
@@ -13301,7 +13307,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="459" spans="2:9">
+    <row r="459" spans="2:9" hidden="1">
       <c r="B459" t="s">
         <v>11</v>
       </c>
@@ -13324,7 +13330,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="460" spans="2:9">
+    <row r="460" spans="2:9" hidden="1">
       <c r="B460" t="s">
         <v>11</v>
       </c>
@@ -13347,7 +13353,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="461" spans="2:9">
+    <row r="461" spans="2:9" hidden="1">
       <c r="B461" t="s">
         <v>11</v>
       </c>
@@ -13370,7 +13376,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="462" spans="2:9">
+    <row r="462" spans="2:9" hidden="1">
       <c r="B462" t="s">
         <v>11</v>
       </c>
@@ -13393,7 +13399,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="463" spans="2:9">
+    <row r="463" spans="2:9" hidden="1">
       <c r="B463" t="s">
         <v>11</v>
       </c>
@@ -13416,7 +13422,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="464" spans="2:9">
+    <row r="464" spans="2:9" hidden="1">
       <c r="B464" t="s">
         <v>11</v>
       </c>
@@ -13439,7 +13445,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="465" spans="2:9">
+    <row r="465" spans="2:9" hidden="1">
       <c r="B465" t="s">
         <v>11</v>
       </c>
@@ -13462,7 +13468,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="466" spans="2:9">
+    <row r="466" spans="2:9" hidden="1">
       <c r="B466" t="s">
         <v>11</v>
       </c>
@@ -13485,7 +13491,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="467" spans="2:9">
+    <row r="467" spans="2:9" hidden="1">
       <c r="B467" t="s">
         <v>11</v>
       </c>
@@ -13505,7 +13511,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="468" spans="2:9">
+    <row r="468" spans="2:9" hidden="1">
       <c r="B468" t="s">
         <v>11</v>
       </c>
@@ -13525,7 +13531,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="469" spans="2:9">
+    <row r="469" spans="2:9" hidden="1">
       <c r="B469" t="s">
         <v>11</v>
       </c>
@@ -13545,7 +13551,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="470" spans="2:9">
+    <row r="470" spans="2:9" hidden="1">
       <c r="B470" t="s">
         <v>11</v>
       </c>
@@ -13568,7 +13574,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="471" spans="2:9">
+    <row r="471" spans="2:9" hidden="1">
       <c r="B471" t="s">
         <v>11</v>
       </c>
@@ -13591,7 +13597,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="472" spans="2:9">
+    <row r="472" spans="2:9" hidden="1">
       <c r="B472" t="s">
         <v>11</v>
       </c>
@@ -13614,7 +13620,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="473" spans="2:9">
+    <row r="473" spans="2:9" hidden="1">
       <c r="B473" t="s">
         <v>11</v>
       </c>
@@ -13637,7 +13643,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="474" spans="2:9">
+    <row r="474" spans="2:9" hidden="1">
       <c r="B474" t="s">
         <v>11</v>
       </c>
@@ -13660,7 +13666,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="475" spans="2:9">
+    <row r="475" spans="2:9" hidden="1">
       <c r="B475" t="s">
         <v>11</v>
       </c>
@@ -13680,7 +13686,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="476" spans="2:9">
+    <row r="476" spans="2:9" hidden="1">
       <c r="B476" t="s">
         <v>11</v>
       </c>
@@ -13700,7 +13706,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="477" spans="2:9">
+    <row r="477" spans="2:9" hidden="1">
       <c r="B477" t="s">
         <v>11</v>
       </c>
@@ -13723,7 +13729,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="478" spans="2:9">
+    <row r="478" spans="2:9" hidden="1">
       <c r="B478" t="s">
         <v>11</v>
       </c>
@@ -13746,7 +13752,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="479" spans="2:9">
+    <row r="479" spans="2:9" hidden="1">
       <c r="B479" t="s">
         <v>11</v>
       </c>
@@ -13769,7 +13775,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="480" spans="2:9">
+    <row r="480" spans="2:9" hidden="1">
       <c r="B480" t="s">
         <v>11</v>
       </c>
@@ -13792,7 +13798,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="481" spans="2:9">
+    <row r="481" spans="2:9" hidden="1">
       <c r="B481" t="s">
         <v>11</v>
       </c>
@@ -13815,7 +13821,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="482" spans="2:9">
+    <row r="482" spans="2:9" hidden="1">
       <c r="B482" t="s">
         <v>11</v>
       </c>
@@ -13838,7 +13844,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="483" spans="2:9">
+    <row r="483" spans="2:9" hidden="1">
       <c r="B483" t="s">
         <v>11</v>
       </c>
@@ -13861,7 +13867,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="484" spans="2:9">
+    <row r="484" spans="2:9" hidden="1">
       <c r="B484" t="s">
         <v>11</v>
       </c>
@@ -13884,7 +13890,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="485" spans="2:9">
+    <row r="485" spans="2:9" hidden="1">
       <c r="B485" t="s">
         <v>11</v>
       </c>
@@ -13907,7 +13913,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="486" spans="2:9">
+    <row r="486" spans="2:9" hidden="1">
       <c r="B486" t="s">
         <v>11</v>
       </c>
@@ -13930,7 +13936,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="487" spans="2:9">
+    <row r="487" spans="2:9" hidden="1">
       <c r="B487" t="s">
         <v>11</v>
       </c>
@@ -13953,7 +13959,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="488" spans="2:9">
+    <row r="488" spans="2:9" hidden="1">
       <c r="B488" t="s">
         <v>11</v>
       </c>
@@ -13973,7 +13979,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="489" spans="2:9">
+    <row r="489" spans="2:9" hidden="1">
       <c r="B489" t="s">
         <v>11</v>
       </c>
@@ -13993,7 +13999,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="490" spans="2:9">
+    <row r="490" spans="2:9" hidden="1">
       <c r="B490" t="s">
         <v>11</v>
       </c>
@@ -14013,7 +14019,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="491" spans="2:9">
+    <row r="491" spans="2:9" hidden="1">
       <c r="B491" t="s">
         <v>11</v>
       </c>
@@ -14033,7 +14039,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="492" spans="2:9">
+    <row r="492" spans="2:9" hidden="1">
       <c r="B492" t="s">
         <v>11</v>
       </c>
@@ -14053,7 +14059,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="493" spans="2:9">
+    <row r="493" spans="2:9" hidden="1">
       <c r="B493" t="s">
         <v>11</v>
       </c>
@@ -14073,7 +14079,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="494" spans="2:9">
+    <row r="494" spans="2:9" hidden="1">
       <c r="B494" t="s">
         <v>11</v>
       </c>
@@ -14093,7 +14099,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="495" spans="2:9">
+    <row r="495" spans="2:9" hidden="1">
       <c r="B495" t="s">
         <v>11</v>
       </c>
@@ -14113,7 +14119,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="496" spans="2:9">
+    <row r="496" spans="2:9" hidden="1">
       <c r="B496" t="s">
         <v>11</v>
       </c>
@@ -14133,7 +14139,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="497" spans="2:9">
+    <row r="497" spans="2:9" hidden="1">
       <c r="B497" t="s">
         <v>11</v>
       </c>
@@ -14153,7 +14159,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="498" spans="2:9">
+    <row r="498" spans="2:9" hidden="1">
       <c r="B498" t="s">
         <v>11</v>
       </c>
@@ -14173,7 +14179,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="499" spans="2:9">
+    <row r="499" spans="2:9" hidden="1">
       <c r="B499" t="s">
         <v>11</v>
       </c>
@@ -14193,7 +14199,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="500" spans="2:9">
+    <row r="500" spans="2:9" hidden="1">
       <c r="B500" t="s">
         <v>11</v>
       </c>
@@ -14213,7 +14219,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="501" spans="2:9">
+    <row r="501" spans="2:9" hidden="1">
       <c r="B501" t="s">
         <v>11</v>
       </c>
@@ -14233,7 +14239,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="502" spans="2:9">
+    <row r="502" spans="2:9" hidden="1">
       <c r="B502" t="s">
         <v>11</v>
       </c>
@@ -14253,7 +14259,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="503" spans="2:9">
+    <row r="503" spans="2:9" hidden="1">
       <c r="B503" t="s">
         <v>11</v>
       </c>
@@ -14276,7 +14282,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="504" spans="2:9">
+    <row r="504" spans="2:9" hidden="1">
       <c r="B504" t="s">
         <v>11</v>
       </c>
@@ -14299,7 +14305,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="505" spans="2:9">
+    <row r="505" spans="2:9" hidden="1">
       <c r="B505" t="s">
         <v>11</v>
       </c>
@@ -14322,7 +14328,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="506" spans="2:9">
+    <row r="506" spans="2:9" hidden="1">
       <c r="B506" t="s">
         <v>11</v>
       </c>
@@ -14345,7 +14351,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="507" spans="2:9">
+    <row r="507" spans="2:9" hidden="1">
       <c r="B507" t="s">
         <v>11</v>
       </c>
@@ -14365,7 +14371,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="508" spans="2:9">
+    <row r="508" spans="2:9" hidden="1">
       <c r="B508" t="s">
         <v>11</v>
       </c>
@@ -14385,7 +14391,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="509" spans="2:9">
+    <row r="509" spans="2:9" hidden="1">
       <c r="B509" t="s">
         <v>11</v>
       </c>
@@ -14405,7 +14411,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="510" spans="2:9">
+    <row r="510" spans="2:9" hidden="1">
       <c r="B510" t="s">
         <v>11</v>
       </c>
@@ -14428,7 +14434,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="511" spans="2:9">
+    <row r="511" spans="2:9" hidden="1">
       <c r="B511" t="s">
         <v>11</v>
       </c>
@@ -14451,7 +14457,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="512" spans="2:9">
+    <row r="512" spans="2:9" hidden="1">
       <c r="B512" t="s">
         <v>11</v>
       </c>
@@ -14474,7 +14480,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="513" spans="2:9">
+    <row r="513" spans="2:9" hidden="1">
       <c r="B513" t="s">
         <v>11</v>
       </c>
@@ -14497,7 +14503,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="514" spans="2:9">
+    <row r="514" spans="2:9" hidden="1">
       <c r="B514" t="s">
         <v>11</v>
       </c>
@@ -14520,7 +14526,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="515" spans="2:9">
+    <row r="515" spans="2:9" hidden="1">
       <c r="B515" t="s">
         <v>11</v>
       </c>
@@ -14543,7 +14549,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="516" spans="2:9">
+    <row r="516" spans="2:9" hidden="1">
       <c r="B516" t="s">
         <v>11</v>
       </c>
@@ -14566,7 +14572,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="517" spans="2:9">
+    <row r="517" spans="2:9" hidden="1">
       <c r="B517" t="s">
         <v>11</v>
       </c>
@@ -14589,7 +14595,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="518" spans="2:9">
+    <row r="518" spans="2:9" hidden="1">
       <c r="B518" t="s">
         <v>11</v>
       </c>
@@ -14612,7 +14618,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="519" spans="2:9">
+    <row r="519" spans="2:9" hidden="1">
       <c r="B519" t="s">
         <v>11</v>
       </c>
@@ -14635,7 +14641,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="520" spans="2:9">
+    <row r="520" spans="2:9" hidden="1">
       <c r="B520" t="s">
         <v>11</v>
       </c>
@@ -14655,7 +14661,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="521" spans="2:9">
+    <row r="521" spans="2:9" hidden="1">
       <c r="B521" t="s">
         <v>11</v>
       </c>
@@ -14675,7 +14681,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="522" spans="2:9">
+    <row r="522" spans="2:9" hidden="1">
       <c r="B522" t="s">
         <v>11</v>
       </c>
@@ -14695,7 +14701,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="523" spans="2:9">
+    <row r="523" spans="2:9" hidden="1">
       <c r="B523" t="s">
         <v>11</v>
       </c>
@@ -14715,7 +14721,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="524" spans="2:9">
+    <row r="524" spans="2:9" hidden="1">
       <c r="B524" t="s">
         <v>11</v>
       </c>
@@ -14735,7 +14741,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="525" spans="2:9">
+    <row r="525" spans="2:9" hidden="1">
       <c r="B525" t="s">
         <v>11</v>
       </c>
@@ -14755,7 +14761,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="526" spans="2:9">
+    <row r="526" spans="2:9" hidden="1">
       <c r="B526" t="s">
         <v>11</v>
       </c>
@@ -14778,7 +14784,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="527" spans="2:9">
+    <row r="527" spans="2:9" hidden="1">
       <c r="B527" t="s">
         <v>11</v>
       </c>
@@ -14801,7 +14807,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="528" spans="2:9">
+    <row r="528" spans="2:9" hidden="1">
       <c r="B528" t="s">
         <v>11</v>
       </c>
@@ -14824,7 +14830,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="529" spans="2:9">
+    <row r="529" spans="2:9" hidden="1">
       <c r="B529" t="s">
         <v>11</v>
       </c>
@@ -14847,7 +14853,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="530" spans="2:9">
+    <row r="530" spans="2:9" hidden="1">
       <c r="B530" t="s">
         <v>11</v>
       </c>
@@ -14867,7 +14873,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="531" spans="2:9">
+    <row r="531" spans="2:9" hidden="1">
       <c r="B531" t="s">
         <v>11</v>
       </c>
@@ -14887,7 +14893,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="532" spans="2:9">
+    <row r="532" spans="2:9" hidden="1">
       <c r="B532" t="s">
         <v>11</v>
       </c>
@@ -14907,7 +14913,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="533" spans="2:9">
+    <row r="533" spans="2:9" hidden="1">
       <c r="B533" t="s">
         <v>11</v>
       </c>
@@ -14927,7 +14933,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="534" spans="2:9">
+    <row r="534" spans="2:9" hidden="1">
       <c r="B534" t="s">
         <v>11</v>
       </c>
@@ -14947,7 +14953,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="535" spans="2:9">
+    <row r="535" spans="2:9" hidden="1">
       <c r="B535" t="s">
         <v>11</v>
       </c>
@@ -14967,7 +14973,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="536" spans="2:9">
+    <row r="536" spans="2:9" hidden="1">
       <c r="B536" t="s">
         <v>11</v>
       </c>
@@ -14990,7 +14996,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="537" spans="2:9">
+    <row r="537" spans="2:9" hidden="1">
       <c r="B537" t="s">
         <v>11</v>
       </c>
@@ -15013,7 +15019,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="538" spans="2:9">
+    <row r="538" spans="2:9" hidden="1">
       <c r="B538" t="s">
         <v>11</v>
       </c>
@@ -15036,7 +15042,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="539" spans="2:9">
+    <row r="539" spans="2:9" hidden="1">
       <c r="B539" t="s">
         <v>11</v>
       </c>
@@ -15059,7 +15065,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="540" spans="2:9">
+    <row r="540" spans="2:9" hidden="1">
       <c r="B540" t="s">
         <v>11</v>
       </c>
@@ -15082,7 +15088,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="541" spans="2:9">
+    <row r="541" spans="2:9" hidden="1">
       <c r="B541" t="s">
         <v>11</v>
       </c>
@@ -15105,7 +15111,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="542" spans="2:9">
+    <row r="542" spans="2:9" hidden="1">
       <c r="B542" t="s">
         <v>11</v>
       </c>
@@ -15128,7 +15134,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="543" spans="2:9">
+    <row r="543" spans="2:9" hidden="1">
       <c r="B543" t="s">
         <v>11</v>
       </c>
@@ -15148,7 +15154,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="544" spans="2:9">
+    <row r="544" spans="2:9" hidden="1">
       <c r="B544" t="s">
         <v>11</v>
       </c>
@@ -15168,7 +15174,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="545" spans="2:9">
+    <row r="545" spans="2:9" hidden="1">
       <c r="B545" t="s">
         <v>11</v>
       </c>
@@ -15188,7 +15194,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="546" spans="2:9">
+    <row r="546" spans="2:9" hidden="1">
       <c r="B546" t="s">
         <v>11</v>
       </c>
@@ -15208,7 +15214,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="547" spans="2:9">
+    <row r="547" spans="2:9" hidden="1">
       <c r="B547" t="s">
         <v>11</v>
       </c>
@@ -15228,7 +15234,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="548" spans="2:9">
+    <row r="548" spans="2:9" hidden="1">
       <c r="B548" t="s">
         <v>11</v>
       </c>
@@ -15248,7 +15254,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="549" spans="2:9">
+    <row r="549" spans="2:9" hidden="1">
       <c r="B549" t="s">
         <v>11</v>
       </c>
@@ -15268,7 +15274,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="550" spans="2:9">
+    <row r="550" spans="2:9" hidden="1">
       <c r="B550" t="s">
         <v>11</v>
       </c>
@@ -15288,7 +15294,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="551" spans="2:9">
+    <row r="551" spans="2:9" hidden="1">
       <c r="B551" t="s">
         <v>11</v>
       </c>
@@ -15308,7 +15314,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="552" spans="2:9">
+    <row r="552" spans="2:9" hidden="1">
       <c r="B552" t="s">
         <v>11</v>
       </c>
@@ -15328,7 +15334,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="553" spans="2:9">
+    <row r="553" spans="2:9" hidden="1">
       <c r="B553" t="s">
         <v>11</v>
       </c>
@@ -15351,7 +15357,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="554" spans="2:9">
+    <row r="554" spans="2:9" hidden="1">
       <c r="B554" t="s">
         <v>11</v>
       </c>
@@ -15374,7 +15380,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="555" spans="2:9">
+    <row r="555" spans="2:9" hidden="1">
       <c r="B555" t="s">
         <v>11</v>
       </c>
@@ -15397,7 +15403,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="556" spans="2:9">
+    <row r="556" spans="2:9" hidden="1">
       <c r="B556" t="s">
         <v>11</v>
       </c>
@@ -15420,7 +15426,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="557" spans="2:9">
+    <row r="557" spans="2:9" hidden="1">
       <c r="B557" t="s">
         <v>11</v>
       </c>
@@ -15443,7 +15449,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="558" spans="2:9">
+    <row r="558" spans="2:9" hidden="1">
       <c r="B558" t="s">
         <v>11</v>
       </c>
@@ -15466,7 +15472,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="559" spans="2:9">
+    <row r="559" spans="2:9" hidden="1">
       <c r="B559" t="s">
         <v>11</v>
       </c>
@@ -15489,7 +15495,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="560" spans="2:9">
+    <row r="560" spans="2:9" hidden="1">
       <c r="B560" t="s">
         <v>11</v>
       </c>
@@ -15509,7 +15515,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="561" spans="2:9">
+    <row r="561" spans="2:9" hidden="1">
       <c r="B561" t="s">
         <v>11</v>
       </c>
@@ -15529,7 +15535,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="562" spans="2:9">
+    <row r="562" spans="2:9" hidden="1">
       <c r="B562" t="s">
         <v>11</v>
       </c>
